--- a/Team-Data/2014-15/3-10-2014-15.xlsx
+++ b/Team-Data/2014-15/3-10-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -772,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>4</v>
@@ -784,10 +851,10 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -799,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -811,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>10</v>
@@ -960,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -981,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1049,13 +1116,13 @@
         <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O4" t="n">
         <v>16.2</v>
@@ -1064,13 +1131,13 @@
         <v>21.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R4" t="n">
         <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
         <v>42.1</v>
@@ -1082,7 +1149,7 @@
         <v>14.3</v>
       </c>
       <c r="W4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>4.2</v>
@@ -1091,37 +1158,37 @@
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.7</v>
+        <v>-3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>20</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1136,13 +1203,13 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>23</v>
@@ -1151,7 +1218,7 @@
         <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
@@ -1169,13 +1236,13 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -1285,28 +1352,28 @@
         <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1336,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,13 +1415,13 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>9</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1530,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.621</v>
+        <v>0.615</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M7" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R7" t="n">
         <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
         <v>14</v>
@@ -1637,22 +1704,22 @@
         <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA7" t="n">
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.9</v>
+        <v>102.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1664,13 +1731,13 @@
         <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,22 +1746,22 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1703,10 +1770,10 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1715,16 +1782,16 @@
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
         <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -1768,13 +1835,13 @@
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>9.199999999999999</v>
@@ -1783,37 +1850,37 @@
         <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>22.4</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1822,16 +1889,16 @@
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,13 +1913,13 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1864,22 +1931,22 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1903,10 +1970,10 @@
         <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2067,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L10" t="n">
         <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0.707</v>
@@ -2165,37 +2232,37 @@
         <v>32.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V10" t="n">
         <v>13.8</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2216,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
         <v>10</v>
@@ -2225,10 +2292,10 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2255,7 +2322,7 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2443,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.677</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2508,25 +2575,25 @@
         <v>11.6</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.8</v>
@@ -2544,22 +2611,22 @@
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,13 +2638,13 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2592,10 +2659,10 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
@@ -2619,10 +2686,10 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
         <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>0.46</v>
+        <v>0.452</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R13" t="n">
         <v>10.6</v>
@@ -2711,10 +2778,10 @@
         <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="U13" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.1</v>
@@ -2726,22 +2793,22 @@
         <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z13" t="n">
         <v>20.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2756,7 +2823,7 @@
         <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>16</v>
@@ -2765,19 +2832,19 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM13" t="n">
         <v>18</v>
       </c>
-      <c r="AM13" t="n">
-        <v>17</v>
-      </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
         <v>13</v>
@@ -2792,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
         <v>14</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2810,13 +2877,13 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3030,25 +3097,25 @@
         <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.274</v>
+        <v>0.258</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
@@ -3060,25 +3127,25 @@
         <v>0.343</v>
       </c>
       <c r="O15" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3123,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3135,25 +3202,25 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3165,19 +3232,19 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3332,7 +3399,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
         <v>19</v>
@@ -3359,10 +3426,10 @@
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3666,7 +3733,7 @@
         <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -3690,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3711,7 +3778,7 @@
         <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3851,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,13 +3948,13 @@
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>8</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -3955,40 +4022,40 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.364</v>
+        <v>0.359</v>
       </c>
       <c r="O20" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.765</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
         <v>13.5</v>
@@ -3997,7 +4064,7 @@
         <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,10 +4073,10 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>0.5</v>
@@ -4036,34 +4103,34 @@
         <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>8</v>
       </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>0.19</v>
+        <v>0.194</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L21" t="n">
         <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N21" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O21" t="n">
         <v>14.4</v>
@@ -4158,7 +4225,7 @@
         <v>18.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
@@ -4170,10 +4237,10 @@
         <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4191,13 +4258,13 @@
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.9</v>
+        <v>-9</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4221,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
@@ -4257,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4397,7 +4464,7 @@
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4418,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -4501,64 +4568,64 @@
         <v>37.4</v>
       </c>
       <c r="J23" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R23" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
         <v>5</v>
@@ -4582,7 +4649,7 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,28 +4673,28 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AT23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4776,7 +4843,7 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4946,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
@@ -4961,13 +5028,13 @@
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ25" t="n">
         <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
@@ -4985,7 +5052,7 @@
         <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,13 +5061,13 @@
         <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -5411,43 +5478,43 @@
         <v>38.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
         <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
@@ -5462,16 +5529,16 @@
         <v>19.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.6</v>
+        <v>101.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
@@ -5492,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,34 +5568,34 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5540,13 +5607,13 @@
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>11</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
         <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J29" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.453</v>
@@ -5605,31 +5672,31 @@
         <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O29" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R29" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U29" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
         <v>7.8</v>
@@ -5638,34 +5705,34 @@
         <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH29" t="n">
         <v>11</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>13</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5695,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5704,28 +5771,28 @@
         <v>25</v>
       </c>
       <c r="AU29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>20</v>
       </c>
-      <c r="AY29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>21</v>
-      </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.449</v>
@@ -5793,13 +5860,13 @@
         <v>16.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
         <v>0.732</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S30" t="n">
         <v>31.8</v>
@@ -5808,7 +5875,7 @@
         <v>43.6</v>
       </c>
       <c r="U30" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
         <v>15.4</v>
@@ -5817,7 +5884,7 @@
         <v>7.3</v>
       </c>
       <c r="X30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
         <v>4.8</v>
@@ -5826,16 +5893,16 @@
         <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
         <v>20</v>
@@ -5862,13 +5929,13 @@
         <v>17</v>
       </c>
       <c r="AM30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN30" t="n">
         <v>18</v>
       </c>
-      <c r="AN30" t="n">
-        <v>17</v>
-      </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
@@ -5880,10 +5947,10 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,10 +5959,10 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6074,7 +6141,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-10-2014-15</t>
+          <t>2015-03-10</t>
         </is>
       </c>
     </row>
